--- a/output/pdf_financials_xlsx/OCI.xlsx
+++ b/output/pdf_financials_xlsx/OCI.xlsx
@@ -4667,40 +4667,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.1857</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.201497</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.260458</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.488697</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.511356</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.283133</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.586133</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.571911</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>4.662528</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.72573</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.823111</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.888382</v>
       </c>
     </row>
     <row r="93">
@@ -7842,7 +7842,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -10512,7 +10516,11 @@
           <t>Reserves 15</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -11568,7 +11576,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -13804,7 +13816,11 @@
           <t>Share-based payment reserve 16</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -14862,7 +14878,11 @@
           <t>Share-based payment reserve 13</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -15312,7 +15332,11 @@
           <t>Share-based payment reserve 12</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -15846,7 +15870,11 @@
           <t>Share-based payment reserve 11</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E125" s="5" t="n">
         <v>2.1857</v>
       </c>

--- a/output/pdf_financials_xlsx/OCI.xlsx
+++ b/output/pdf_financials_xlsx/OCI.xlsx
@@ -859,13 +859,13 @@
         <v>0.192021</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.18975</v>
+        <v>1.632131</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.390516</v>
+        <v>3.81118</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.2952</v>
+        <v>1.085034</v>
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
@@ -873,13 +873,13 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.320115</v>
+        <v>0.496905</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.441793</v>
+        <v>2.76442</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.55464</v>
+        <v>1.045082</v>
       </c>
       <c r="M10" s="1" t="inlineStr">
         <is>
@@ -910,13 +910,13 @@
         <v>-0.192021</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.18975</v>
+        <v>-1.632131</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.390516</v>
+        <v>-3.81118</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.2952</v>
+        <v>-1.085034</v>
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.039095</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -979,13 +979,13 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.056774</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.227943</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.049298</v>
       </c>
       <c r="M12" s="1" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.750642</v>
+        <v>-0.789737</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.290193</v>
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.780393</v>
+        <v>-2.55245</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>10.076814</v>
+        <v>10.126112</v>
       </c>
       <c r="M27" s="1" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.750642</v>
+        <v>-0.789737</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.290193</v>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.780393</v>
+        <v>-2.55245</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>10.076814</v>
+        <v>10.126112</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -2099,40 +2099,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.111353</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.093898</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.198593</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.321835</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.331528</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.49226</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.332687</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>6.094388</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>5.533174</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.140181</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.536671</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.015284</v>
       </c>
     </row>
     <row r="35">
@@ -2185,40 +2185,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>2.6115</v>
+        <v>2.722853</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.6115</v>
+        <v>0.705398</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.198593</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.321835</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.632258</v>
+        <v>0.963786</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.49226</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.332687</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.496809</v>
+        <v>8.591196999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.966963</v>
+        <v>6.500137</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.140181</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-9.210570000000001</v>
+        <v>-8.673899</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>-0.801212</v>
+        <v>-0.785928</v>
       </c>
     </row>
     <row r="37">
@@ -2701,40 +2701,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.157182</v>
+        <v>0.045829</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.095642</v>
+        <v>0.001744</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.204206</v>
+        <v>0.005613</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.410641</v>
+        <v>0.088806</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.422834</v>
+        <v>0.091306</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.078527</v>
+        <v>0.586267</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.9422199999999999</v>
+        <v>0.609533</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>6.71894</v>
+        <v>0.624552</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>6.238676</v>
+        <v>0.705502</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>5.7521</v>
+        <v>4.611919</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>25.842993</v>
+        <v>25.306322</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>20.783138</v>
+        <v>20.767854</v>
       </c>
     </row>
     <row r="49">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -12704,7 +12704,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
@@ -28272,7 +28272,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -28654,7 +28654,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -29850,7 +29850,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -30232,7 +30232,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -31436,7 +31436,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -35244,7 +35244,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">

--- a/output/pdf_financials_xlsx/OCI.xlsx
+++ b/output/pdf_financials_xlsx/OCI.xlsx
@@ -3437,13 +3437,13 @@
         <v>0</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.023843</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.262194</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.034172</v>
       </c>
       <c r="M64" s="3" t="n">
         <v>0</v>
@@ -5028,19 +5028,19 @@
         <v>0.079165</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.009108</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.064816</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.094611</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>-0.006364</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>-0.060027</v>
       </c>
       <c r="I101" s="3" t="n">
         <v>-0.170566</v>
@@ -5243,19 +5243,19 @@
         <v>0.096691</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.053267</v>
+        <v>-0.044159</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.045196</v>
+        <v>-0.01962</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.044253</v>
+        <v>0.050358</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.04098</v>
+        <v>-0.047344</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.369738</v>
+        <v>0.309711</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>-0.299748</v>
@@ -5421,7 +5421,7 @@
         <v>0</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.014801</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
@@ -5433,16 +5433,16 @@
         <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>-0.021957</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.113947</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.015086</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="111">
@@ -5630,7 +5630,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.6115</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -5639,7 +5639,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.815506</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
@@ -16474,7 +16474,11 @@
           <t>Accretion expense 10</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -18732,7 +18736,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -19868,7 +19876,11 @@
           <t>Accretion 13</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -22940,7 +22952,11 @@
           <t>GST-HST receivable</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -23080,7 +23096,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -25572,7 +25592,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -26176,7 +26200,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -26252,7 +26280,11 @@
           <t>Proceeds from short-term investments</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
